--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -233,46 +233,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
     <t>QUIAHUA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
     <t>PANZO</t>
   </si>
   <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>JACOBO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>JOANNA JAQUELINE</t>
   </si>
   <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
+    <t>LUIS ALFREDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>JONATHAN MICHEL</t>
   </si>
   <si>
+    <t>JOACIM ALBERTO</t>
+  </si>
+  <si>
     <t>DIEGO JOSUE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
 </sst>
 </file>
@@ -818,28 +836,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -875,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD4">
         <v>5</v>
@@ -919,28 +937,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -967,19 +985,19 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>5</v>
@@ -1020,28 +1038,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1074,13 +1092,13 @@
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE6">
         <v>8</v>
@@ -1121,28 +1139,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1181,7 +1199,7 @@
         <v>10</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE7">
         <v>10</v>
@@ -1222,28 +1240,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1279,10 +1297,10 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8">
         <v>8</v>
@@ -1323,28 +1341,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1371,7 +1389,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <v>6</v>
@@ -1424,28 +1442,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1472,22 +1490,22 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF10">
         <v>6</v>
@@ -1525,28 +1543,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1585,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE11">
         <v>8</v>
@@ -1626,28 +1644,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1680,13 +1698,13 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE12">
         <v>9</v>
@@ -1727,28 +1745,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1775,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1787,7 +1805,7 @@
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13">
         <v>10</v>
@@ -1828,28 +1846,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1882,16 +1900,16 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF14">
         <v>9</v>
@@ -1929,28 +1947,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1977,7 +1995,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1989,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="AD15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE15">
         <v>10</v>
@@ -2030,28 +2048,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2078,7 +2096,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -2087,13 +2105,13 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF16">
         <v>8</v>
@@ -2131,28 +2149,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2191,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE17">
         <v>10</v>
@@ -2232,28 +2250,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2280,19 +2298,19 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>10</v>
       </c>
       <c r="AD18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE18">
         <v>8</v>
@@ -2333,28 +2351,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2390,10 +2408,10 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19">
         <v>5</v>
@@ -2434,28 +2452,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2482,7 +2500,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>6</v>
@@ -2494,7 +2512,7 @@
         <v>8</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>8</v>
@@ -2535,28 +2553,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2583,22 +2601,22 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21">
         <v>7</v>
@@ -2636,28 +2654,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2684,13 +2702,13 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2699,7 +2717,7 @@
         <v>7</v>
       </c>
       <c r="AE22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF22">
         <v>8</v>
@@ -2737,28 +2755,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2791,16 +2809,16 @@
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD23">
         <v>6</v>
       </c>
       <c r="AE23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>9</v>
@@ -2838,28 +2856,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2886,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2895,13 +2913,13 @@
         <v>9</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>8</v>
@@ -2939,28 +2957,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2987,7 +3005,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2996,13 +3014,13 @@
         <v>6</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF25">
         <v>6</v>
@@ -3040,28 +3058,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3088,7 +3106,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -3100,10 +3118,10 @@
         <v>10</v>
       </c>
       <c r="AD26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>9</v>
@@ -3141,28 +3159,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3198,10 +3216,10 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE27">
         <v>9</v>
@@ -3242,28 +3260,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3290,7 +3308,7 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3299,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD28">
         <v>7</v>
@@ -3343,28 +3361,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3391,22 +3409,22 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF29">
         <v>5</v>
@@ -3444,28 +3462,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3501,13 +3519,13 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD30">
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF30">
         <v>6</v>
@@ -3545,28 +3563,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3602,10 +3620,10 @@
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE31">
         <v>6</v>
@@ -3646,28 +3664,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3703,7 +3721,7 @@
         <v>9</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD32">
         <v>6</v>
@@ -3747,28 +3765,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3810,7 +3828,7 @@
         <v>7</v>
       </c>
       <c r="AE33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF33">
         <v>10</v>
@@ -3848,28 +3866,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3905,10 +3923,10 @@
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE34">
         <v>10</v>
@@ -3949,28 +3967,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3997,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -4006,13 +4024,13 @@
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF35">
         <v>10</v>
@@ -4050,28 +4068,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4104,16 +4122,16 @@
         <v>5</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD36">
         <v>6</v>
       </c>
       <c r="AE36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF36">
         <v>7</v>
@@ -4291,16 +4309,16 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -4315,16 +4333,16 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="W4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X4">
         <v>100</v>
@@ -4362,22 +4380,22 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K5">
         <v>93.3</v>
       </c>
       <c r="L5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O5">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P5">
         <v>85</v>
@@ -4386,22 +4404,22 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S5">
         <v>93.3</v>
       </c>
       <c r="T5">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W5">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X5">
         <v>85</v>
@@ -4608,7 +4626,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -4632,7 +4650,7 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X8">
         <v>100</v>
@@ -4753,7 +4771,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4762,7 +4780,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P10">
         <v>90</v>
@@ -4777,7 +4795,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4786,7 +4804,7 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X10">
         <v>90</v>
@@ -4901,13 +4919,13 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4916,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4925,13 +4943,13 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4940,7 +4958,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -5070,7 +5088,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -5094,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -5375,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -5399,7 +5417,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="W18">
         <v>100</v>
@@ -5440,22 +5458,22 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K19">
         <v>93.3</v>
       </c>
       <c r="L19">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O19">
-        <v>55.6</v>
+        <v>75.8</v>
       </c>
       <c r="P19">
         <v>65</v>
@@ -5464,22 +5482,22 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S19">
         <v>93.3</v>
       </c>
       <c r="T19">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W19">
-        <v>55.6</v>
+        <v>75.8</v>
       </c>
       <c r="X19">
         <v>65</v>
@@ -5683,10 +5701,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O22">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5707,10 +5725,10 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W22">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -5760,10 +5778,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O23">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -5784,10 +5802,10 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W23">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -5837,10 +5855,10 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O24">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5861,10 +5879,10 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W24">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X24">
         <v>100</v>
@@ -5985,13 +6003,13 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -6009,13 +6027,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W26">
         <v>100</v>
@@ -6222,10 +6240,10 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O29">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P29">
         <v>90</v>
@@ -6246,10 +6264,10 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W29">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X29">
         <v>90</v>
@@ -6293,16 +6311,16 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O30">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6317,16 +6335,16 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U30">
         <v>100</v>
       </c>
       <c r="V30">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W30">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -6364,19 +6382,19 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -6388,19 +6406,19 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W31">
         <v>100</v>
@@ -6518,7 +6536,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -6533,7 +6551,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6542,7 +6560,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6557,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="W33">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X33">
         <v>100</v>
@@ -6607,7 +6625,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6631,7 +6649,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W34">
         <v>100</v>
@@ -6687,7 +6705,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -6711,7 +6729,7 @@
         <v>100</v>
       </c>
       <c r="W35">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X35">
         <v>100</v>
@@ -6761,10 +6779,10 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O36">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -6785,10 +6803,10 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W36">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X36">
         <v>100</v>
@@ -6892,16 +6910,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>69.7</v>
+        <v>81.8</v>
       </c>
       <c r="G3" s="2">
-        <v>30.3</v>
+        <v>18.2</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -6924,19 +6942,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6947,7 +6965,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6956,19 +6974,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6979,7 +6997,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6988,19 +7006,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>84.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>15.2</v>
+        <v>9.1</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7043,7 +7061,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -7052,19 +7070,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7146,7 +7164,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7178,22 +7196,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7201,22 +7219,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7224,16 +7242,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920371</v>
+        <v>24330051920271</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7247,16 +7265,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920371</v>
+        <v>24330051920271</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -7270,22 +7288,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920385</v>
+        <v>24330051920312</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7293,22 +7311,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920385</v>
+        <v>24330051920312</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7322,10 +7340,10 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -7345,10 +7363,10 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -7362,24 +7380,70 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920380</v>
+        <v>24330051920371</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920384</v>
+      </c>
+      <c r="B11" t="s">
         <v>76</v>
       </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920385</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -239,58 +239,31 @@
     <t>LEON</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>YEPEZ</t>
   </si>
   <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
     <t>JOANNA JAQUELINE</t>
   </si>
   <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
-    <t>LUIS ALFREDO</t>
-  </si>
-  <si>
     <t>YAEL</t>
   </si>
   <si>
-    <t>JONATHAN MICHEL</t>
-  </si>
-  <si>
     <t>JOACIM ALBERTO</t>
-  </si>
-  <si>
-    <t>DIEGO JOSUE</t>
   </si>
 </sst>
 </file>
@@ -839,7 +812,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -854,7 +827,7 @@
         <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -940,7 +913,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -955,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1041,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1056,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1089,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1142,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1157,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1243,7 +1216,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1258,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1291,7 +1264,7 @@
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>9</v>
@@ -1344,7 +1317,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -1359,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1392,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1445,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1460,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1493,7 +1466,7 @@
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1508,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1546,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1561,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1647,7 +1620,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1662,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1695,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1748,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1763,7 +1736,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1796,7 +1769,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1811,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1849,7 +1822,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1864,7 +1837,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1950,7 +1923,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1965,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1998,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -2051,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -2066,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -2152,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2167,7 +2140,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2200,7 +2173,7 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
@@ -2253,7 +2226,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2268,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2301,7 +2274,7 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2354,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2369,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2455,7 +2428,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2470,7 +2443,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2556,7 +2529,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2571,7 +2544,7 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2604,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2619,7 +2592,7 @@
         <v>7</v>
       </c>
       <c r="AF21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2657,7 +2630,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2672,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2705,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2758,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2773,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2821,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="AF23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2859,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2874,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2907,7 +2880,7 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>9</v>
@@ -2922,7 +2895,7 @@
         <v>8</v>
       </c>
       <c r="AF24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2960,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2975,7 +2948,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -3008,7 +2981,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>6</v>
@@ -3023,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3061,7 +3034,7 @@
         <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -3076,7 +3049,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -3109,7 +3082,7 @@
         <v>8</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -3124,7 +3097,7 @@
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3162,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -3177,7 +3150,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -3210,7 +3183,7 @@
         <v>9</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>9</v>
@@ -3263,7 +3236,7 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -3278,7 +3251,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -3364,7 +3337,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -3379,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -3412,7 +3385,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>7</v>
@@ -3427,7 +3400,7 @@
         <v>6</v>
       </c>
       <c r="AF29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3465,7 +3438,7 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -3480,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3528,7 +3501,7 @@
         <v>6</v>
       </c>
       <c r="AF30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3566,7 +3539,7 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -3581,7 +3554,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3667,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3682,7 +3655,7 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3715,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -3768,7 +3741,7 @@
         <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3783,7 +3756,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3869,7 +3842,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3884,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3917,7 +3890,7 @@
         <v>9</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3970,7 +3943,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3985,7 +3958,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -4018,7 +3991,7 @@
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>9</v>
@@ -4071,7 +4044,7 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -4086,7 +4059,7 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -4383,7 +4356,7 @@
         <v>90</v>
       </c>
       <c r="K5">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L5">
         <v>88.59999999999999</v>
@@ -4398,7 +4371,7 @@
         <v>97</v>
       </c>
       <c r="P5">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4407,7 +4380,7 @@
         <v>90</v>
       </c>
       <c r="S5">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="T5">
         <v>88.59999999999999</v>
@@ -4422,7 +4395,7 @@
         <v>97</v>
       </c>
       <c r="X5">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4783,7 +4756,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4807,7 +4780,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X10">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -4845,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4860,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4869,7 +4842,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4884,7 +4857,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -4937,7 +4910,7 @@
         <v>97</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4961,7 +4934,7 @@
         <v>97</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -5014,7 +4987,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5038,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="X13">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -5091,7 +5064,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5115,7 +5088,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -5461,7 +5434,7 @@
         <v>85</v>
       </c>
       <c r="K19">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L19">
         <v>79.5</v>
@@ -5476,7 +5449,7 @@
         <v>75.8</v>
       </c>
       <c r="P19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5485,7 +5458,7 @@
         <v>85</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="T19">
         <v>79.5</v>
@@ -5500,7 +5473,7 @@
         <v>75.8</v>
       </c>
       <c r="X19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -5769,7 +5742,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5784,7 +5757,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5793,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5808,7 +5781,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -5846,7 +5819,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5870,7 +5843,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5938,7 +5911,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5962,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -6169,7 +6142,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6193,7 +6166,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -6231,7 +6204,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -6246,7 +6219,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -6255,7 +6228,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6270,7 +6243,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -6323,7 +6296,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6347,7 +6320,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X30">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -6385,7 +6358,7 @@
         <v>95</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L31">
         <v>97.7</v>
@@ -6400,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -6409,7 +6382,7 @@
         <v>95</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T31">
         <v>97.7</v>
@@ -6424,7 +6397,7 @@
         <v>100</v>
       </c>
       <c r="X31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y31">
         <v>100</v>
@@ -6878,19 +6851,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>69.7</v>
+        <v>78.8</v>
       </c>
       <c r="G2" s="2">
-        <v>30.3</v>
+        <v>21.2</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7050,7 +7023,7 @@
         <v>6.1</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7164,7 +7137,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7202,10 +7175,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
         <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7225,10 +7198,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7248,10 +7221,10 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7271,10 +7244,10 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -7288,22 +7261,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920312</v>
+        <v>24330051920381</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
         <v>80</v>
       </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7311,22 +7284,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920312</v>
+        <v>24330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
         <v>80</v>
       </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7334,116 +7307,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920381</v>
+        <v>24330051920384</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920381</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920371</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920384</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920385</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -233,6 +233,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -252,6 +258,9 @@
   </si>
   <si>
     <t>BELLO</t>
+  </si>
+  <si>
+    <t>ANDY ARELY</t>
   </si>
   <si>
     <t>JOANNA JAQUELINE</t>
@@ -6404,7 +6413,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6436,22 +6445,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920382</v>
+        <v>24330051920028</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6459,22 +6468,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920382</v>
+        <v>24330051920028</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6482,22 +6491,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920271</v>
+        <v>24330051920028</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6505,16 +6514,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6528,22 +6537,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920381</v>
+        <v>24330051920382</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6551,22 +6560,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920381</v>
+        <v>24330051920271</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6574,24 +6583,93 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
+        <v>24330051920271</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920381</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920381</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
         <v>24330051920384</v>
       </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
         <v>63</v>
       </c>
-      <c r="G8">
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -203,21 +203,21 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -233,46 +233,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>YEPEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>BELLO</t>
   </si>
   <si>
+    <t>YOSHUA RAFAEL</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
     <t>ANDY ARELY</t>
   </si>
   <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
+    <t>JOACIM ALBERTO</t>
+  </si>
+  <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>JOACIM ALBERTO</t>
   </si>
 </sst>
 </file>
@@ -778,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -820,13 +829,13 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -847,7 +856,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -909,13 +918,13 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -936,7 +945,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z5">
         <v>7</v>
@@ -998,13 +1007,13 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1087,13 +1096,13 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1176,13 +1185,13 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1265,13 +1274,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1354,13 +1363,13 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1443,13 +1452,13 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1464,7 +1473,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1532,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1621,13 +1630,13 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1668,7 +1677,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1710,13 +1719,13 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1731,7 +1740,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1799,13 +1808,13 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1888,13 +1897,13 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1909,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1977,13 +1986,13 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2066,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2093,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2113,7 +2122,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -2155,13 +2164,13 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2244,13 +2253,13 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2333,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2360,7 +2369,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2422,13 +2431,13 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2443,13 +2452,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z22">
         <v>10</v>
@@ -2511,13 +2520,13 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2532,13 +2541,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2600,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2647,7 +2656,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -2689,13 +2698,13 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2710,13 +2719,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>9</v>
@@ -2778,13 +2787,13 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2867,13 +2876,13 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2888,7 +2897,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2956,13 +2965,13 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3003,7 +3012,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -3045,13 +3054,13 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3066,7 +3075,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3092,7 +3101,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -3134,13 +3143,13 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3161,7 +3170,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3181,7 +3190,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -3223,13 +3232,13 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3250,7 +3259,7 @@
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3312,13 +3321,13 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3333,7 +3342,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3401,13 +3410,13 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3422,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3490,13 +3499,13 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3579,13 +3588,13 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3626,7 +3635,7 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -3668,13 +3677,13 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3689,13 +3698,13 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>7</v>
@@ -3879,13 +3888,13 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3947,13 +3956,13 @@
         <v>86.40000000000001</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
         <v>86.7</v>
       </c>
       <c r="R5">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4151,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4293,7 +4302,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4423,13 +4432,13 @@
         <v>97.7</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4899,13 +4908,13 @@
         <v>75</v>
       </c>
       <c r="P19">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q19">
         <v>86.7</v>
       </c>
       <c r="R19">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S19">
         <v>50</v>
@@ -5103,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5171,7 +5180,7 @@
         <v>95.5</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
         <v>96.7</v>
@@ -5381,7 +5390,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5443,7 +5452,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5579,7 +5588,7 @@
         <v>95.5</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
         <v>93.3</v>
@@ -5653,7 +5662,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5715,13 +5724,13 @@
         <v>95.5</v>
       </c>
       <c r="P31">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q31">
         <v>93.3</v>
       </c>
       <c r="R31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5851,7 +5860,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6171,19 +6180,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>81.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>18.2</v>
+        <v>12.1</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6194,7 +6203,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6203,16 +6212,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -6226,7 +6235,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6247,7 +6256,7 @@
         <v>9.1</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6258,7 +6267,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6267,19 +6276,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6290,7 +6299,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6311,7 +6320,7 @@
         <v>6.1</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6322,7 +6331,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -6331,19 +6340,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G8" s="2">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6413,7 +6422,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6445,16 +6454,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920028</v>
+        <v>24330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6468,16 +6477,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920028</v>
+        <v>24330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6491,22 +6500,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920028</v>
+        <v>24330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6514,22 +6523,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920382</v>
+        <v>24330051920259</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6543,16 +6552,16 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6560,22 +6569,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6583,22 +6592,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920271</v>
+        <v>24330051920028</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6606,22 +6615,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920381</v>
+        <v>24330051920028</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6629,16 +6638,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920381</v>
+        <v>24330051920271</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6658,18 +6667,41 @@
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920381</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -203,21 +203,21 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -233,49 +233,67 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>YEPEZ</t>
   </si>
   <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
+    <t>MARIA</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
+    <t>NESTOR NOE</t>
+  </si>
+  <si>
     <t>YOSHUA RAFAEL</t>
   </si>
   <si>
+    <t>ANDY ARELY</t>
+  </si>
+  <si>
     <t>JOANNA JAQUELINE</t>
   </si>
   <si>
-    <t>ANDY ARELY</t>
-  </si>
-  <si>
     <t>CRISTHIAN GAEL</t>
+  </si>
+  <si>
+    <t>ISAI</t>
   </si>
   <si>
     <t>JOACIM ALBERTO</t>
@@ -841,13 +859,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -862,13 +880,13 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -930,13 +948,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -951,13 +969,13 @@
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1019,13 +1037,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1040,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>8</v>
@@ -1108,13 +1126,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1197,13 +1215,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1218,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1286,13 +1304,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1375,13 +1393,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1464,13 +1482,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1553,13 +1571,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1574,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1642,13 +1660,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1731,13 +1749,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1752,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1820,13 +1838,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1909,13 +1927,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1998,13 +2016,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2087,13 +2105,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2108,7 +2126,7 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <v>8</v>
@@ -2176,13 +2194,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2265,13 +2283,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2354,13 +2372,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2443,13 +2461,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2464,10 +2482,10 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2532,13 +2550,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2559,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2621,13 +2639,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2642,7 +2660,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>8</v>
@@ -2710,13 +2728,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2734,10 +2752,10 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2799,13 +2817,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2888,13 +2906,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2909,13 +2927,13 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2977,13 +2995,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2998,7 +3016,7 @@
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3066,13 +3084,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3087,10 +3105,10 @@
         <v>8</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3155,13 +3173,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3176,10 +3194,10 @@
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3244,13 +3262,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3268,7 +3286,7 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3333,13 +3351,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3354,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -3422,13 +3440,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3443,7 +3461,7 @@
         <v>10</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>10</v>
@@ -3511,13 +3529,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3600,13 +3618,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3689,13 +3707,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -3710,7 +3728,7 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>7</v>
@@ -3900,10 +3918,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3968,13 +3986,13 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U5">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V5">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4175,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4311,10 +4329,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4382,7 +4400,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4447,10 +4465,10 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4518,7 +4536,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4583,10 +4601,10 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4852,7 +4870,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>55</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -4920,13 +4938,13 @@
         <v>50</v>
       </c>
       <c r="T19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U19">
-        <v>75.8</v>
+        <v>83.3</v>
       </c>
       <c r="V19">
-        <v>75</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5124,10 +5142,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U22">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5192,13 +5210,13 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U23">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5260,10 +5278,10 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U24">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5334,7 +5352,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5396,7 +5414,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -5470,7 +5488,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5538,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5600,13 +5618,13 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U29">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5668,13 +5686,13 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U30">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V30">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5736,13 +5754,13 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5875,7 +5893,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5940,7 +5958,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -6011,7 +6029,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6076,10 +6094,10 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U36">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6203,7 +6221,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -6224,7 +6242,7 @@
         <v>9.1</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6235,7 +6253,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6244,19 +6262,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6267,7 +6285,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -6276,19 +6294,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G6" s="2">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6299,7 +6317,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6308,19 +6326,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G7" s="2">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6331,7 +6349,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -6352,7 +6370,7 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6422,7 +6440,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6454,16 +6472,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920259</v>
+        <v>24330051920009</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6477,16 +6495,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920259</v>
+        <v>24330051920009</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6500,22 +6518,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920259</v>
+        <v>24330051920009</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6526,19 +6544,19 @@
         <v>24330051920259</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6546,16 +6564,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920382</v>
+        <v>24330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6569,22 +6587,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920382</v>
+        <v>24330051920259</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6598,10 +6616,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6621,10 +6639,10 @@
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6638,16 +6656,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B10" t="s">
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6661,22 +6679,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920384</v>
+        <v>24330051920271</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6684,24 +6702,70 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920381</v>
+        <v>24330051920019</v>
       </c>
       <c r="B12" t="s">
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920384</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920381</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="G12">
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20241.xlsx
+++ b/grupos/1FM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
@@ -239,67 +239,34 @@
     <t>RUIZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
     <t>PIEDRAS</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
+    <t>MARIA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
     <t>NESTOR NOE</t>
   </si>
   <si>
     <t>YOSHUA RAFAEL</t>
   </si>
   <si>
+    <t>ISAI</t>
+  </si>
+  <si>
     <t>ANDY ARELY</t>
-  </si>
-  <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
-    <t>CRISTHIAN GAEL</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>JOACIM ALBERTO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
 </sst>
 </file>
@@ -850,13 +817,13 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -871,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -939,13 +906,13 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -960,13 +927,13 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1028,13 +995,13 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1055,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1117,13 +1084,13 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1138,13 +1105,13 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1206,13 +1173,13 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1227,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1295,13 +1262,13 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1316,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1384,13 +1351,13 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1411,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1473,13 +1440,13 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1500,7 +1467,7 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1562,13 +1529,13 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1651,13 +1618,13 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1740,13 +1707,13 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1761,13 +1728,13 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1829,13 +1796,13 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1918,13 +1885,13 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1945,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -2007,13 +1974,13 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2096,13 +2063,13 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2123,7 +2090,7 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>5</v>
@@ -2185,13 +2152,13 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2274,13 +2241,13 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2363,13 +2330,13 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2452,13 +2419,13 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2541,13 +2508,13 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2568,7 +2535,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>6</v>
@@ -2630,13 +2597,13 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2651,13 +2618,13 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>9</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2719,13 +2686,13 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2746,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2808,13 +2775,13 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2829,13 +2796,13 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -2897,13 +2864,13 @@
         <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2924,7 +2891,7 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2986,13 +2953,13 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3013,7 +2980,7 @@
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>8</v>
@@ -3075,13 +3042,13 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -3096,13 +3063,13 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3164,13 +3131,13 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3185,13 +3152,13 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3253,13 +3220,13 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3274,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3342,13 +3309,13 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3363,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3431,13 +3398,13 @@
         <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3458,7 +3425,7 @@
         <v>9</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3520,13 +3487,13 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3547,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <v>9</v>
@@ -3609,13 +3576,13 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3630,13 +3597,13 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>9</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA35">
         <v>8</v>
@@ -3698,13 +3665,13 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3719,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3909,13 +3876,13 @@
         <v>87.5</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R4">
         <v>96.90000000000001</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T4">
         <v>90.59999999999999</v>
@@ -3977,13 +3944,13 @@
         <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R5">
         <v>92.2</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T5">
         <v>96.90000000000001</v>
@@ -4385,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4929,13 +4896,13 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Q19">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R19">
         <v>85.90000000000001</v>
       </c>
       <c r="S19">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="T19">
         <v>96.90000000000001</v>
@@ -5201,7 +5168,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5269,7 +5236,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5609,7 +5576,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5745,7 +5712,7 @@
         <v>93.8</v>
       </c>
       <c r="Q31">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R31">
         <v>98.40000000000001</v>
@@ -6157,7 +6124,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -6166,19 +6133,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>78.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>21.2</v>
+        <v>12.1</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6189,7 +6156,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -6198,19 +6165,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>87.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>12.1</v>
+        <v>6.1</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6230,19 +6197,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6253,7 +6220,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6262,19 +6229,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="G5" s="2">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6440,7 +6407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6478,16 +6445,16 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6501,16 +6468,16 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6518,22 +6485,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920009</v>
+        <v>24330051920259</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6547,13 +6514,13 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -6564,22 +6531,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920259</v>
+        <v>24330051920019</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6587,185 +6554,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920259</v>
+        <v>24330051920028</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920028</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920028</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920382</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920271</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920019</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920384</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920381</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>
